--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-13).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-13).xlsx
@@ -935,13 +935,13 @@
     <t>214</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 9.033,52</t>
-  </si>
-  <si>
-    <t>99.0</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 9.012,32</t>
+  </si>
+  <si>
+    <t>98.8</t>
   </si>
   <si>
     <t>65.6</t>
@@ -953,13 +953,13 @@
     <t>21.9</t>
   </si>
   <si>
-    <t>8.6</t>
+    <t>8.7</t>
   </si>
   <si>
     <t>6.1</t>
   </si>
   <si>
-    <t>32.0%</t>
+    <t>32.1%</t>
   </si>
   <si>
     <t>17.5%</t>
@@ -7613,7 +7613,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7643,14 +7643,26 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
+      <c r="M42" s="5">
+        <v>5111.9300000000003</v>
+      </c>
+      <c r="N42" s="6">
+        <v>63</v>
+      </c>
       <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
+      <c r="P42" s="7">
+        <v>6.7954306451612911</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>23.158805660377357</v>
+      </c>
+      <c r="R42" s="8">
+        <v>10.489795918367347</v>
+      </c>
       <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
+      <c r="T42" s="9">
+        <v>0.18867924528301888</v>
+      </c>
       <c r="U42" s="9"/>
       <c r="V42" s="9"/>
       <c r="W42" s="9"/>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-13).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-13).xlsx
@@ -935,40 +935,40 @@
     <t>214</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 9.012,32</t>
-  </si>
-  <si>
-    <t>98.8</t>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 9.018,65</t>
+  </si>
+  <si>
+    <t>98.9</t>
   </si>
   <si>
     <t>65.6</t>
   </si>
   <si>
-    <t>6.54</t>
-  </si>
-  <si>
-    <t>21.9</t>
-  </si>
-  <si>
-    <t>8.7</t>
-  </si>
-  <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>32.1%</t>
-  </si>
-  <si>
-    <t>17.5%</t>
+    <t>6.52</t>
+  </si>
+  <si>
+    <t>21.8</t>
+  </si>
+  <si>
+    <t>8.6</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>31.8%</t>
+  </si>
+  <si>
+    <t>17.3%</t>
   </si>
   <si>
     <t>1.6%</t>
   </si>
   <si>
-    <t>0.6%</t>
+    <t>0.5%</t>
   </si>
   <si>
     <t>3.5%</t>
@@ -980,46 +980,46 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>5.6%</t>
-  </si>
-  <si>
-    <t>2.4%</t>
-  </si>
-  <si>
     <t>5.5%</t>
   </si>
   <si>
-    <t>2469.0</t>
-  </si>
-  <si>
-    <t>2080.0</t>
-  </si>
-  <si>
-    <t>186.0</t>
+    <t>2.3%</t>
+  </si>
+  <si>
+    <t>5.4%</t>
+  </si>
+  <si>
+    <t>2488.0</t>
+  </si>
+  <si>
+    <t>2096.0</t>
+  </si>
+  <si>
+    <t>194.0</t>
   </si>
   <si>
     <t>66.0</t>
   </si>
   <si>
-    <t>416.0</t>
-  </si>
-  <si>
-    <t>135.0</t>
-  </si>
-  <si>
-    <t>26.0</t>
-  </si>
-  <si>
-    <t>667.0</t>
+    <t>419.0</t>
+  </si>
+  <si>
+    <t>136.0</t>
+  </si>
+  <si>
+    <t>27.0</t>
+  </si>
+  <si>
+    <t>671.0</t>
   </si>
   <si>
     <t>283.0</t>
   </si>
   <si>
-    <t>653.0</t>
-  </si>
-  <si>
-    <t>0.9%</t>
+    <t>655.0</t>
+  </si>
+  <si>
+    <t>0.8%</t>
   </si>
   <si>
     <t>103.0</t>
@@ -7649,7 +7649,9 @@
       <c r="N42" s="6">
         <v>63</v>
       </c>
-      <c r="O42" s="6"/>
+      <c r="O42" s="6">
+        <v>53</v>
+      </c>
       <c r="P42" s="7">
         <v>6.7954306451612911</v>
       </c>
@@ -7659,31 +7661,75 @@
       <c r="R42" s="8">
         <v>10.489795918367347</v>
       </c>
-      <c r="S42" s="8"/>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
       <c r="T42" s="9">
         <v>0.18867924528301888</v>
       </c>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="U42" s="9">
+        <v>0.075471698113207544</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.075471698113207544</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -10011,7 +10057,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -10041,35 +10087,93 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
-      <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="M58" s="5">
+        <v>10188.700000000001</v>
+      </c>
+      <c r="N58" s="6">
+        <v>122</v>
+      </c>
+      <c r="O58" s="6">
+        <v>94</v>
+      </c>
+      <c r="P58" s="7">
+        <v>2.721311475409836</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>16.371808510638299</v>
+      </c>
+      <c r="R58" s="8">
+        <v>6.6842202127659567</v>
+      </c>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
+      <c r="T58" s="9">
+        <v>0.47872340425531917</v>
+      </c>
+      <c r="U58" s="9">
+        <v>0.10638297872340426</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.063829787234042548</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.021276595744680851</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0.010638297872340425</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0.021276595744680851</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>6</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -17860,7 +17964,9 @@
       <c r="N111" s="6">
         <v>22</v>
       </c>
-      <c r="O111" s="6"/>
+      <c r="O111" s="6">
+        <v>21</v>
+      </c>
       <c r="P111" s="7">
         <v>8.9060590909090909</v>
       </c>
@@ -17870,31 +17976,75 @@
       <c r="R111" s="8">
         <v>1.8015857142857143</v>
       </c>
-      <c r="S111" s="8"/>
+      <c r="S111" s="8">
+        <v>7</v>
+      </c>
       <c r="T111" s="9">
         <v>0.23809523809523808</v>
       </c>
-      <c r="U111" s="9"/>
-      <c r="V111" s="9"/>
-      <c r="W111" s="9"/>
-      <c r="X111" s="9"/>
-      <c r="Y111" s="9"/>
-      <c r="Z111" s="9"/>
-      <c r="AA111" s="9"/>
-      <c r="AB111" s="9"/>
-      <c r="AC111" s="9"/>
-      <c r="AD111" s="6"/>
-      <c r="AE111" s="6"/>
-      <c r="AF111" s="6"/>
-      <c r="AG111" s="6"/>
-      <c r="AH111" s="6"/>
-      <c r="AI111" s="6"/>
-      <c r="AJ111" s="6"/>
-      <c r="AK111" s="6"/>
-      <c r="AL111" s="6"/>
-      <c r="AM111" s="6"/>
-      <c r="AN111" s="9"/>
-      <c r="AO111" s="6"/>
+      <c r="U111" s="9">
+        <v>0</v>
+      </c>
+      <c r="V111" s="9">
+        <v>0</v>
+      </c>
+      <c r="W111" s="9">
+        <v>0</v>
+      </c>
+      <c r="X111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO111" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP111" s="4">
         <v>58</v>
       </c>
@@ -28054,7 +28204,9 @@
       <c r="N179" s="6">
         <v>148</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>86</v>
+      </c>
       <c r="P179" s="7">
         <v>4.8444073825503358</v>
       </c>
@@ -28064,31 +28216,75 @@
       <c r="R179" s="8">
         <v>1.3242244186046512</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.7558139534883721</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0.023255813953488372</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0.023255813953488372</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-13).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-13).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>R$ 9.018,65</t>
-  </si>
-  <si>
-    <t>98.9</t>
-  </si>
-  <si>
-    <t>65.6</t>
-  </si>
-  <si>
-    <t>6.52</t>
-  </si>
-  <si>
-    <t>21.8</t>
-  </si>
-  <si>
-    <t>8.6</t>
-  </si>
-  <si>
-    <t>6.2</t>
-  </si>
-  <si>
-    <t>31.8%</t>
-  </si>
-  <si>
-    <t>17.3%</t>
+    <t>21</t>
+  </si>
+  <si>
+    <t>R$ 8.991,76</t>
+  </si>
+  <si>
+    <t>98.6</t>
+  </si>
+  <si>
+    <t>65.2</t>
+  </si>
+  <si>
+    <t>6.51</t>
+  </si>
+  <si>
+    <t>21.9</t>
+  </si>
+  <si>
+    <t>8.7</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>32.7%</t>
+  </si>
+  <si>
+    <t>17.2%</t>
   </si>
   <si>
     <t>1.6%</t>
@@ -989,10 +989,10 @@
     <t>5.4%</t>
   </si>
   <si>
-    <t>2488.0</t>
-  </si>
-  <si>
-    <t>2096.0</t>
+    <t>2490.0</t>
+  </si>
+  <si>
+    <t>2098.0</t>
   </si>
   <si>
     <t>194.0</t>
@@ -1001,7 +1001,7 @@
     <t>66.0</t>
   </si>
   <si>
-    <t>419.0</t>
+    <t>421.0</t>
   </si>
   <si>
     <t>136.0</t>
@@ -2209,7 +2209,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2239,14 +2239,26 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
+      <c r="M6" s="5">
+        <v>18918.279999999999</v>
+      </c>
+      <c r="N6" s="6">
+        <v>194</v>
+      </c>
       <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
+      <c r="P6" s="7">
+        <v>6.0056410256410251</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>16.486372352941178</v>
+      </c>
+      <c r="R6" s="8">
+        <v>3.5378698224852068</v>
+      </c>
       <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
+      <c r="T6" s="9">
+        <v>0.41176470588235292</v>
+      </c>
       <c r="U6" s="9"/>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -4907,7 +4919,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -4937,14 +4949,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>8922.8799999999992</v>
+      </c>
+      <c r="N24" s="6">
+        <v>104</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>3.8980582524271843</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>22.332723170731708</v>
+      </c>
+      <c r="R24" s="8">
+        <v>11.387398780487805</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.13414634146341464</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -6731,7 +6755,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6761,35 +6785,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>6641.3699999999999</v>
+      </c>
+      <c r="N36" s="6">
+        <v>76</v>
+      </c>
+      <c r="O36" s="6">
+        <v>64</v>
+      </c>
+      <c r="P36" s="7">
+        <v>5.5638157894736846</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>17.26953125</v>
+      </c>
+      <c r="R36" s="8">
+        <v>4.5942703125</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.453125</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -9020,7 +9102,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9050,35 +9132,93 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
-      <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
-      <c r="U51" s="9"/>
-      <c r="V51" s="9"/>
-      <c r="W51" s="9"/>
-      <c r="X51" s="9"/>
-      <c r="Y51" s="9"/>
-      <c r="Z51" s="9"/>
-      <c r="AA51" s="9"/>
-      <c r="AB51" s="9"/>
-      <c r="AC51" s="9"/>
-      <c r="AD51" s="6"/>
-      <c r="AE51" s="6"/>
-      <c r="AF51" s="6"/>
-      <c r="AG51" s="6"/>
-      <c r="AH51" s="6"/>
-      <c r="AI51" s="6"/>
-      <c r="AJ51" s="6"/>
-      <c r="AK51" s="6"/>
-      <c r="AL51" s="6"/>
-      <c r="AM51" s="6"/>
-      <c r="AN51" s="9"/>
-      <c r="AO51" s="6"/>
+      <c r="M51" s="5">
+        <v>1675.1400000000001</v>
+      </c>
+      <c r="N51" s="6">
+        <v>16</v>
+      </c>
+      <c r="O51" s="6">
+        <v>10</v>
+      </c>
+      <c r="P51" s="7">
+        <v>8.3197937500000005</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>52.161670000000001</v>
+      </c>
+      <c r="R51" s="8">
+        <v>34.67333</v>
+      </c>
+      <c r="S51" s="8">
+        <v>7</v>
+      </c>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
+      <c r="U51" s="9">
+        <v>0</v>
+      </c>
+      <c r="V51" s="9">
+        <v>0</v>
+      </c>
+      <c r="W51" s="9">
+        <v>0</v>
+      </c>
+      <c r="X51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP51" s="4">
         <v>58</v>
       </c>
@@ -14722,7 +14862,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14750,14 +14890,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>9012.3600000000006</v>
+      </c>
+      <c r="N89" s="6">
+        <v>89</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>7.1934862068965515</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>21.310145652173912</v>
+      </c>
+      <c r="R89" s="8">
+        <v>6.4914822222222215</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.17391304347826086</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -25051,7 +25203,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25081,14 +25233,26 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
+      <c r="M158" s="5">
+        <v>3780.0100000000002</v>
+      </c>
+      <c r="N158" s="6">
+        <v>41</v>
+      </c>
       <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
+      <c r="P158" s="7">
+        <v>5.4788609756097557</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>19.207575757575757</v>
+      </c>
+      <c r="R158" s="8">
+        <v>7.1732333333333331</v>
+      </c>
       <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
+      <c r="T158" s="9">
+        <v>0.27272727272727271</v>
+      </c>
       <c r="U158" s="9"/>
       <c r="V158" s="9"/>
       <c r="W158" s="9"/>
